--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1783,57 +1783,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,109 +1845,109 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Batı Mısır Kök Kurdu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Diabrotica virgifera</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1957,29 +1957,29 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1999,17 +1999,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2024,54 +2024,54 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2143,44 +2143,44 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2205,29 +2205,29 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2272,24 +2272,24 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2341,17 +2341,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2403,17 +2403,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2589,17 +2589,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2651,17 +2651,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2713,17 +2713,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2899,17 +2899,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2961,32 +2961,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,39 +3016,39 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3073,44 +3073,44 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3135,59 +3135,59 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3197,34 +3197,34 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3264,29 +3264,29 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,7 +3333,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,37 +3343,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3395,47 +3395,47 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3457,32 +3457,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3507,59 +3507,59 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3569,44 +3569,44 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3616,22 +3616,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3643,17 +3643,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,32 +3767,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,42 +3829,42 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3891,17 +3891,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3953,42 +3953,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4015,42 +4015,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4325,47 +4325,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SOYA</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Soya sap sineği</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Melanagromyza sojae</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>30 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>30 ml/daLarva</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,05 - 0,05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4375,59 +4375,59 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>SOYA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Soya sap sineği</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Melanagromyza sojae</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/daLarva</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,05 - 0,05</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4449,32 +4449,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4511,7 +4511,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4521,52 +4521,52 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Kurşuni Küf</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Botrytis sp.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4697,52 +4697,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Phytophthora infestans</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>60 g/100 l su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,54 +4752,54 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4814,24 +4814,24 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>400 g/100 L su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4883,32 +4883,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,44 +4918,44 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>1000 g/100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4965,27 +4965,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5193,17 +5193,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5213,27 +5213,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5255,17 +5255,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5275,27 +5275,27 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5332,22 +5332,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5518,22 +5518,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5565,17 +5565,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5585,27 +5585,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5627,47 +5627,47 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5709,22 +5709,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5895,17 +5895,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5952,27 +5952,27 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6019,22 +6019,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6076,22 +6076,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6185,17 +6185,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6205,27 +6205,27 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6247,17 +6247,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6267,27 +6267,27 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6324,17 +6324,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6453,27 +6453,27 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6495,47 +6495,47 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6557,17 +6557,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6577,27 +6577,27 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6619,17 +6619,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6639,27 +6639,27 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6763,17 +6763,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6805,60 +6805,122 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>QUADRİS</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>250 g/l Azoxystrobin</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>FESLEĞEN</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>KÜLLEME</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Erysiphe spp.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>45 ml/da</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>70 mg / kg</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Fungisit</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>KARATE ZEON</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>CS</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>ISPANAK</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>Spodoptera littoralis</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>7 Gün</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>15 ml/da</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>0.6 mg/kg</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,37 +481,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -536,24 +536,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -635,17 +635,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,22 +667,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,12 +791,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1039,32 +1039,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,32 +1116,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1845,57 +1845,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1907,109 +1907,109 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Batı Mısır Kök Kurdu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Diabrotica virgifera</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2019,29 +2019,29 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2086,54 +2086,54 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2205,44 +2205,44 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2267,29 +2267,29 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2403,17 +2403,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2423,12 +2423,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2651,17 +2651,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2713,17 +2713,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2775,17 +2775,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2961,17 +2961,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3023,32 +3023,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,39 +3078,39 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3135,44 +3135,44 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3197,59 +3197,59 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,37 +3405,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,59 +3445,59 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3519,32 +3519,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3643,57 +3643,57 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3750,74 +3750,74 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,32 +3829,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3891,42 +3891,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4015,42 +4015,42 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4077,42 +4077,42 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4387,47 +4387,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SOYA</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Soya sap sineği</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Melanagromyza sojae</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>30 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>30 ml/daLarva</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,05 - 0,05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4437,59 +4437,59 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>SOYA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Soya sap sineği</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Melanagromyza sojae</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/daLarva</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,05 - 0,05</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4511,32 +4511,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4583,99 +4583,99 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kurşuni Küf</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Botrytis sp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>600 g/100 L su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4685,34 +4685,34 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4722,22 +4722,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Phytophthora infestans</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>60 g/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Cyprodinil: 0,02 mg/kg Fludioxonil: 0,01* mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4747,44 +4747,44 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4794,22 +4794,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4821,124 +4821,124 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>400 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1000 g/100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Kükürt ve mineral yağ kullanımı ile ilgili bitki koruma ürünü etiketinde yer alan kullanım uyarılarına dikkat edilmelidi.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5084,32 +5084,32 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5208,22 +5208,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5255,47 +5255,47 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5317,47 +5317,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5394,32 +5394,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5518,22 +5518,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5627,47 +5627,47 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5719,12 +5719,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5766,17 +5766,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5890,17 +5890,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5937,47 +5937,47 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6014,32 +6014,32 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6076,22 +6076,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6138,17 +6138,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6185,47 +6185,47 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6247,47 +6247,47 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6309,47 +6309,47 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6448,17 +6448,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6495,47 +6495,47 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6557,52 +6557,52 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6611,316 +6611,6 @@
         </is>
       </c>
       <c r="L100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>APRIN XL 350 ES</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>350 g/l Metalaxyl-m</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Toprak kökenli patojenler</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>50 ml/100 kg tohum</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3 mg/kg</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Alternaria yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Alternaria spp.</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>KÜLLEME</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Erysiphe spp.</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>70 mg / kg</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>KARATE ZEON</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>ISPANAK</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Pamuk yaprakkurdu</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Spodoptera littoralis</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>7 Gün</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>15 ml/da</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>0.6 mg/kg</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,29 +3326,29 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3581,47 +3581,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,69 +3631,69 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3705,79 +3705,79 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3797,17 +3797,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2334,24 +2334,24 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2396,24 +2396,24 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2527,17 +2527,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2713,17 +2713,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2775,17 +2775,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2837,17 +2837,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3023,17 +3023,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3085,32 +3085,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,29 +3326,29 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
@@ -3596,17 +3596,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ZEYTİN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Zeytin pasakarları</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Aculus oleariu, Aceria oleae</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>400  g/100 L su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3626,64 +3626,64 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Akarisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3693,44 +3693,44 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3740,22 +3740,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,17 +3767,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3797,17 +3797,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,57 +481,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -543,218 +543,218 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -764,59 +764,59 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -826,59 +826,59 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -888,59 +888,59 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -950,59 +950,59 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1012,22 +1012,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1039,32 +1039,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1101,57 +1101,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1163,57 +1163,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1225,119 +1225,119 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1349,57 +1349,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1411,57 +1411,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1473,57 +1473,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1535,57 +1535,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1597,57 +1597,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1659,57 +1659,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1721,57 +1721,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1783,57 +1783,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,57 +1845,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1969,32 +1969,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2004,89 +2004,89 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2118,32 +2118,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2155,47 +2155,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2205,69 +2205,69 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2279,57 +2279,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2341,171 +2341,171 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2520,39 +2520,39 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2604,32 +2604,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2644,54 +2644,54 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2706,54 +2706,54 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,14 +2768,14 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2785,37 +2785,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2830,59 +2830,59 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,39 +2892,39 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,59 +2954,59 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,59 +3016,59 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,59 +3078,59 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,54 +3140,54 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3197,59 +3197,59 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3259,59 +3259,59 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3348,32 +3348,32 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3395,12 +3395,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,59 +3445,59 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3519,47 +3519,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3581,57 +3581,57 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ZEYTİN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Zeytin pasakarları</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aculus oleariu, Aceria oleae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>400  g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3643,47 +3643,47 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3693,24 +3693,24 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3720,32 +3720,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3767,57 +3767,57 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3829,57 +3829,57 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3891,57 +3891,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3953,62 +3953,62 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Batı Mısır Kök Kurdu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Diabrotica virgifera</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -4030,27 +4030,27 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4060,64 +4060,64 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4154,27 +4154,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4216,27 +4216,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4251,54 +4251,54 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4313,54 +4313,54 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4375,54 +4375,54 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4437,59 +4437,59 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SOYA</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Soya sap sineği</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Melanagromyza sojae</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>30 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>30 ml/daLarva</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0,05 - 0,05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4499,44 +4499,44 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4561,44 +4561,44 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>600 g/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4618,49 +4618,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,136 +4670,136 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4836,32 +4836,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4871,19 +4871,19 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4893,37 +4893,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4933,44 +4933,44 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4980,12 +4980,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4995,59 +4995,59 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5057,69 +5057,69 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5131,119 +5131,119 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,32 +5255,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5290,84 +5290,84 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5379,57 +5379,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5441,57 +5441,57 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,57 +5503,57 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5565,119 +5565,119 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5704,17 +5704,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5751,47 +5751,47 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5813,57 +5813,57 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5875,57 +5875,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5937,57 +5937,57 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5999,57 +5999,57 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6061,556 +6061,370 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>KİVİ</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>250 g /100 L</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SOYA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Soya sap sineği</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Melanagromyza sojae</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>30 gün</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>30 ml/daLarva</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>0,05 - 0,05</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>70 mg/kg</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>FESLEĞEN</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>KÜLLEME</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Erysiphe spp.</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>45 ml/da</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>70 mg / kg</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>KARATE ZEON</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>ISPANAK</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Pamuk yaprakkurdu</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Spodoptera littoralis</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>7 Gün</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>15 ml/da</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>0.6 mg/kg</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2527,32 +2527,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>400 ml/100 L su</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2577,96 +2577,96 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2706,29 +2706,29 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2775,22 +2775,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2805,17 +2805,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2837,22 +2837,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2909,12 +2909,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2929,17 +2929,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2954,39 +2954,39 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3016,54 +3016,54 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,39 +3078,39 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,47 +3147,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3224,32 +3224,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3891,57 +3891,57 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3953,12 +3953,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4003,106 +4003,106 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Batı Mısır Kök Kurdu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Diabrotica virgifera</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -4154,17 +4154,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4189,59 +4189,59 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4263,32 +4263,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4313,44 +4313,44 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4375,29 +4375,29 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4573,17 +4573,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,17 +4697,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4759,17 +4759,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4821,17 +4821,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5007,17 +5007,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5069,32 +5069,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5124,39 +5124,39 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
@@ -5208,17 +5208,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5255,7 +5255,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5265,37 +5265,37 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5310,54 +5310,54 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5434,54 +5434,54 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5503,47 +5503,47 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5565,47 +5565,47 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5615,59 +5615,59 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5689,119 +5689,119 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5813,52 +5813,52 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5875,42 +5875,42 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5937,42 +5937,42 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6014,27 +6014,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6076,27 +6076,27 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6106,59 +6106,59 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KİVİ</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>250 g /100 L</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6371,47 +6371,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SOYA</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Soya sap sineği</t>
+          <t>Yalancı Kelebek</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Melanagromyza sojae</t>
+          <t>Ricania japonica</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>30 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>30 ml/daLarva</t>
+          <t>250 g/100 L su</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0,05 - 0,05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6421,12 +6421,74 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>THIOVIT JET</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>%80 Kükürt</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>KİVİ</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yalancı Kelebek</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ricania japonica</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>7 gün</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>250 g /100 L</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2589,32 +2589,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2634,49 +2634,49 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,24 +2768,24 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2899,22 +2899,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,54 +3078,54 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,32 +3209,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4015,57 +4015,57 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4077,109 +4077,109 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Batı Mısır Kök Kurdu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Diabrotica virgifera</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4189,29 +4189,29 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4256,54 +4256,54 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4375,44 +4375,44 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4437,29 +4437,29 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4504,24 +4504,24 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4573,17 +4573,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4635,17 +4635,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4821,17 +4821,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4945,17 +4945,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5007,7 +5007,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5069,7 +5069,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5193,32 +5193,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5248,39 +5248,39 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5305,44 +5305,44 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5367,59 +5367,59 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5429,34 +5429,34 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5496,29 +5496,29 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5565,7 +5565,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5575,37 +5575,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5627,47 +5627,47 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5689,32 +5689,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5739,59 +5739,59 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5801,44 +5801,44 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5848,22 +5848,22 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5875,17 +5875,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5905,17 +5905,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5937,32 +5937,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5999,42 +5999,42 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6061,17 +6061,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6123,42 +6123,42 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6185,42 +6185,42 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NARENCİYE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6448,45 +6448,107 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>MISIR</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Yalancı Kelebek</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ricania japonica</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>7 gün</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>250 g/100 L su</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>THIOVIT JET</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>%80 Kükürt</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
           <t>KİVİ</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Yalancı Kelebek</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>Ricania japonica</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>7 gün</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>250 g /100 L</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -2713,12 +2713,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,17 +2743,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,24 +2768,24 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2899,22 +2899,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5441,22 +5441,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5496,29 +5496,29 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5533,17 +5533,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2465,57 +2465,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>LATİN ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2527,57 +2527,57 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>ELEKTRİK ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>400 ml/100 L su</t>
+          <t>45ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2589,109 +2589,109 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>TURUNÇGİLLER</t>
+          <t>MENEKŞE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Topak unlubiti</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nipaecoccus viridis</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1500 ml/ 100 L su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>SAP KEREVİZİ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Cercospora sp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2701,49 +2701,49 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,54 +2768,54 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>400 ml/100 L su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2825,136 +2825,136 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3023,22 +3023,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,39 +3140,39 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3202,39 +3202,39 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3286,32 +3286,32 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,54 +3326,54 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3383,59 +3383,59 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3445,59 +3445,59 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3534,32 +3534,32 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4077,57 +4077,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4189,59 +4189,59 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4251,59 +4251,59 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4325,109 +4325,109 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Batı Mısır Kök Kurdu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Diabrotica virgifera</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4437,44 +4437,44 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4499,59 +4499,59 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4561,44 +4561,44 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4623,44 +4623,44 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4685,29 +4685,29 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4752,24 +4752,24 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,17 +4945,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5007,17 +5007,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5069,17 +5069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5255,32 +5255,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,39 +5310,39 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5362,49 +5362,49 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5424,126 +5424,126 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5565,7 +5565,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5575,37 +5575,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5620,54 +5620,54 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5689,47 +5689,47 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5751,47 +5751,47 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5828,32 +5828,32 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5863,69 +5863,69 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5937,32 +5937,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5999,32 +5999,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6049,69 +6049,69 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6123,52 +6123,52 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6185,32 +6185,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>YABAN MERSİNİ</t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6247,42 +6247,42 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NARENCİYE</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6297,54 +6297,54 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6354,17 +6354,17 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6386,27 +6386,27 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6416,59 +6416,59 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Yalancı Kelebek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ricania japonica</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>250 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6510,45 +6510,293 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>NARENCİYE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Yalancı Kelebek</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ricania japonica</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>7 gün</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>250 g/100 L su</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>THIOVIT JET</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>%80 Kükürt</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>FASULYE</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Yalancı Kelebek</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ricania japonica</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>7 gün</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>250 g/100 L su</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>THIOVIT JET</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>%80 Kükürt</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>HIYAR</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Yalancı Kelebek</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Ricania japonica</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>7 gün</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>250 g/100 L su</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>THIOVIT JET</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>%80 Kükürt</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>MISIR</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Yalancı Kelebek</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ricania japonica</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>7 gün</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>250 g/100 L su</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>İnsektisit</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>THIOVIT JET</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>WG</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>%80 Kükürt</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
           <t>KİVİ</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Yalancı Kelebek</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>Ricania japonica</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>7 gün</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>250 g /100 L</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>İnsektisit</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Menekşe için düzenlenmiştir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -2961,12 +2961,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3016,29 +3016,29 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -5689,22 +5689,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5744,29 +5744,29 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5843,17 +5843,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -2837,32 +2837,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TURUNÇGİLLER</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Topak unlubiti</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nipaecoccus viridis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1500 ml/ 100 L su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2882,49 +2882,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2944,29 +2944,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3016,29 +3016,29 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4387,47 +4387,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Batı Mısır Kök Kurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Diabrotica virgifera</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4437,29 +4437,29 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Edirne, Kırklareli, Tekirdağ illeri için geçici tavsiye verilmiştir.</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4479,17 +4479,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,54 +4504,54 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>İNCİR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>400 g/ 100 l su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4623,44 +4623,44 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4685,29 +4685,29 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4752,24 +4752,24 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4821,17 +4821,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5069,17 +5069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5193,17 +5193,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5255,7 +5255,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5379,17 +5379,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5441,32 +5441,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,39 +5496,39 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>AGRIMEC EC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>18 g/l Abamectin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>PALMİYE, HURMA, SKAS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Rhynchophorus ferrugineus</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>50 - 100 ml / 1 L su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5553,44 +5553,44 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5615,59 +5615,59 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dut kabuklubiti</t>
+          <t>Kahverengi kokarca</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pseudaulacaspis pentagona</t>
+          <t>Halyomorpha halys</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1000 ml/100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5677,34 +5677,34 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5744,29 +5744,29 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5813,7 +5813,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5823,37 +5823,37 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kahverengi kokarca</t>
+          <t>KAVUN SİNEĞİ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Halyomorpha halys</t>
+          <t>Myiopardalis pardalina</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>35 gün</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/da Ergin</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5875,47 +5875,47 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KAVUN SİNEĞİ</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Myiopardalis pardalina</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>35 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>30 ml/da Ergin</t>
+          <t>1500 ml/100 l su</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5937,32 +5937,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Kırmızı örümcekler</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Tetranychus spp.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1500 ml/100 l su</t>
+          <t>400 g/100 l su</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5987,59 +5987,59 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6049,44 +6049,44 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6096,22 +6096,22 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6123,17 +6123,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6185,32 +6185,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6247,42 +6247,42 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6309,17 +6309,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6371,42 +6371,42 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NAR</t>
+          <t>YABAN MERSİNİ</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kırmızıörümcekler</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>600 g/ 100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6416,389 +6416,17 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Fungisit + Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>YABAN MERSİNİ</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Turunçgil unlubiti</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Planococcus citri</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>1000 ml/100 l su</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NARENCİYE</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Yalancı Kelebek</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Ricania japonica</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>7 gün</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>250 g/100 L su</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>FASULYE</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Yalancı Kelebek</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Ricania japonica</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>7 gün</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>250 g/100 L su</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>HIYAR</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Yalancı Kelebek</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Ricania japonica</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>7 gün</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>250 g/100 L su</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>MISIR</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Yalancı Kelebek</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Ricania japonica</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>7 gün</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>250 g/100 L su</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>KİVİ</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Yalancı Kelebek</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Ricania japonica</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>7 gün</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>250 g /100 L</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Ordu, Giresun,Trabzon ve Rize illeri için geçerlidir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6368,68 +6368,6 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>YABAN MERSİNİ</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Turunçgil unlubiti</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Planococcus citri</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>1000 ml/100 l su</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için düzenlenmiştir.</t>
+          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Menekşe için düzenlenmiştir.</t>
+          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5937,47 +5937,47 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t xml:space="preserve">PAMUK </t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kırmızı örümcekler</t>
+          <t>Pamuk unlubiti</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tetranychus spp.</t>
+          <t>Phenacoccus solenopsis</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>400 g/100 l su</t>
+          <t>50 ml/da</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5987,44 +5987,44 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Kükürt içeren bitki koruma ürünlerinin kullanımında ürün etiketinde yer alan uyarılara dikkat edilmelidir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6034,22 +6034,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6061,17 +6061,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6123,32 +6123,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6185,42 +6185,42 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6247,17 +6247,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6301,68 +6301,6 @@
         </is>
       </c>
       <c r="L95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NAR</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Kırmızıörümcekler</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>600 g/ 100 L su</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Fungisit + Akarisit</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2837,32 +2837,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2882,49 +2882,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TURUNÇGİLLER</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Topak unlubiti</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nipaecoccus viridis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1500 ml/ 100 L su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2944,29 +2944,29 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3016,29 +3016,29 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,12 +3271,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -5627,22 +5627,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5657,17 +5657,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5682,29 +5682,29 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
@@ -5937,32 +5937,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAMUK </t>
+          <t>BEZELYE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Pamuk unlubiti</t>
+          <t>Bezelye pası</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Phenacoccus solenopsis</t>
+          <t>Uromyces pisi</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5972,22 +5972,22 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>50 ml/da</t>
+          <t>80 ml/da</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5999,17 +5999,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6029,17 +6029,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>80 ml/da</t>
+          <t>300 g/100 l su</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6061,32 +6061,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BEZELYE</t>
+          <t>KAVAK</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bezelye pası</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Uromyces pisi</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>300 g/100 l su</t>
+          <t>50 ml/100 l su (Larva- Ergin)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6123,42 +6123,42 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KAVAK</t>
+          <t>NAR</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Kırmızıörümcekler</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Tetranychus spp., Panonychus spp.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>---</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
+          <t>1500 ml/100 L su</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -6185,17 +6185,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1500 ml/100 L su</t>
+          <t>600 g/ 100 L su</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit + Akarisit</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6239,68 +6239,6 @@
         </is>
       </c>
       <c r="L94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NAR</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Kırmızıörümcekler</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>600 g/ 100 L su</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Fungisit + Akarisit</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,47 +481,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>MAXİM XL 035 FS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>25 g/l Fludioxonil + 10 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MERCİMEK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Fide kök çürüklüğü (Çökerten)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Rhizoctonia solani, Fusarium spp., Pythium spp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>200 ml /100 kg tohum</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>Fludioxonil: 0,4, Metalaxyl-m: 0,01*</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -531,12 +531,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kışlık ekim</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,17 +667,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -729,47 +729,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -853,47 +853,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -977,47 +977,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1101,47 +1101,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1163,47 +1163,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1349,47 +1349,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1798,17 +1798,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2113,22 +2113,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2155,17 +2155,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2217,52 +2217,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>LATİN ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2356,27 +2356,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ELEKTRİK ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MENEKŞE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2480,17 +2480,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LATİN ÇİÇEĞİ</t>
+          <t>SAP KEREVİZİ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Cercospora sp.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2542,32 +2542,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ELEKTRİK ÇİÇEĞİ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>45ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MENEKŞE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2666,22 +2666,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAP KEREVİZİ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>YAPRAK LEKESİ</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cercospora sp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2706,39 +2706,39 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ŞEFTALİ - NEKTARİN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2775,47 +2775,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CEVİZ</t>
+          <t>ŞEFTALİ - NEKTARİN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>400 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2837,32 +2837,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>TURUNÇGİLLER</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Topak unlubiti</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nipaecoccus viridis</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1500 ml/ 100 L su</t>
+          <t>400 ml/100 L su</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2882,49 +2882,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2944,49 +2944,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3085,7 +3085,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,24 +3140,24 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3395,32 +3395,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3519,32 +3519,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4325,57 +4325,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4387,79 +4387,79 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>TRABZON HURMASI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Mycosphaerella nawae</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4479,17 +4479,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,54 +4504,54 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>İNCİR</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>400 g/ 100 l su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -5867,378 +5867,6 @@
         </is>
       </c>
       <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>TRABZON HURMASI</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Turunçgil unlubiti</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Planococcus citri</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>1500 ml/100 l su</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>QUADRİS</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>250 g/l Azoxystrobin</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>BEZELYE</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Bezelye pası</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Uromyces pisi</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>7 gün</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>80 ml/da</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>3 mg/kg</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>BEZELYE</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Bezelye pası</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Uromyces pisi</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>300 g/100 l su</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>AMPLİGO 150 ZC</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>ZC</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>KAVAK</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Dipkurtları</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Capnodis spp.</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>50 ml/100 l su (Larva- Ergin)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NAR</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Kırmızıörümcekler</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>1500 ml/100 L su</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>İnsektisit+Akarisit</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>THIOVIT JET</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>%80 Kükürt</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NAR</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Kırmızıörümcekler</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Tetranychus spp., Panonychus spp.</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>600 g/ 100 L su</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Fungisit + Akarisit</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -543,52 +543,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -729,17 +729,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -791,47 +791,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1039,47 +1039,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1163,47 +1163,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1411,47 +1411,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,32 +1550,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1999,17 +1999,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2175,22 +2175,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LATİN ÇİÇEĞİ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2356,32 +2356,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ELEKTRİK ÇİÇEĞİ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>45ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,22 +2418,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MENEKŞE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SAP KEREVİZİ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>YAPRAK LEKESİ</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cercospora sp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>LATİN ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2604,32 +2604,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ELEKTRİK ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2666,22 +2666,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MENEKŞE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -2728,22 +2728,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>SAP KEREVİZİ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Cercospora sp.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5627,22 +5627,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5657,17 +5657,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5682,29 +5682,29 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -543,52 +543,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -729,17 +729,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -749,27 +749,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -791,47 +791,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1039,47 +1039,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1163,47 +1163,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1225,47 +1225,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1411,47 +1411,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,32 +1550,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1860,17 +1860,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1999,17 +1999,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2175,22 +2175,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2232,22 +2232,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2465,52 +2465,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,29 +3140,29 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,14 +3388,14 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4690,24 +4690,24 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4752,24 +4752,24 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4821,17 +4821,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5069,17 +5069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5193,17 +5193,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5255,7 +5255,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5379,17 +5379,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SWITCH 62.5 WG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>30 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5441,32 +5441,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5810,68 +5810,6 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>IMPERATOR 25 EC</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>250 g/l Cypermethrin</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>KAVUN</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>KAVUN SİNEĞİ</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Myiopardalis pardalina</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>35 gün</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>30 ml/da Ergin</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -2217,52 +2217,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2465,52 +2465,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,29 +3140,29 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,14 +3388,14 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5627,22 +5627,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MISIR</t>
+          <t>ERİK</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5657,17 +5657,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>50 ml / da</t>
+          <t>30 ml/100 L su</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
+          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5682,29 +5682,29 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ERİK</t>
+          <t>ÇELTİK</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5719,17 +5719,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>28 gün</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>30 ml/100 L su</t>
+          <t>30 ml/da</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
+          <t>0,2 mg/kg</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ÇELTİK</t>
+          <t>MISIR</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5781,17 +5781,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>28 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>30 ml/da</t>
+          <t>50 ml / da</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0,2 mg/kg</t>
+          <t>MRL bilgisi açıklamada yer almaktadır.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,32 +5503,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AGRIMEC EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>18 g/l Abamectin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PALMİYE, HURMA, SKAS</t>
+          <t>CEVİZ</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PALMİYE KIRMIZIBÖCEĞİ</t>
+          <t>Dut kabuklubiti</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rhynchophorus ferrugineus</t>
+          <t>Pseudaulacaspis pentagona</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>50 - 100 ml / 1 L su</t>
+          <t>1000 ml/100 L su</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5553,260 +5553,12 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sadece süs bitkileri amacıyla yetiştirilen Palmiye, Hurma, Skas bitkilerinde uygulanmalıdır, gıda amacıyla yetiştiriciliği yapılan Palmiye ve Hurma bitkilerinde uygulanmamalıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>CEVİZ</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Dut kabuklubiti</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Pseudaulacaspis pentagona</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>1000 ml/100 L su</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>AMPLİGO 150 ZC</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>ZC</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>ERİK</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Kahverengi kokarca</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Halyomorpha halys</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>14 Gün</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>30 ml/100 L su</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Chlorantraniliprole: 1; Lambda-cyhalothrin: 0,2</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>NİNJA 5 EC</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>ÇELTİK</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kahverengi kokarca</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Halyomorpha halys</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>28 gün</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>30 ml/da</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>0,2 mg/kg</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>NİNJA 5 EC</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>MISIR</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Kahverengi kokarca</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Halyomorpha halys</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>14 gün</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>50 ml / da</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>MRL bilgisi açıklamada yer almaktadır.</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>MRL mg/kg : (0234000 Taze mısır: 0.05) (0500030 Tohumluk mısır: 0.02)</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4387,79 +4387,79 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TRABZON HURMASI</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TRABZON HURMASINDA YAPRAK LEKESİ</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mycosphaerella nawae</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>70 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>80-100 l/da (Dekara 50-100 L su ile )</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4479,17 +4479,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4504,54 +4504,54 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4561,44 +4561,44 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4650,17 +4650,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4690,24 +4690,24 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4752,24 +4752,24 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4821,17 +4821,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5069,17 +5069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5193,17 +5193,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5255,7 +5255,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5317,7 +5317,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5379,17 +5379,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5435,130 +5435,6 @@
       <c r="L81" t="inlineStr">
         <is>
           <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>SWITCH 62.5 WG</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SÜS BİTKİLERİ</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>30 g/100 L su</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>PLOCAFİR</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>700 g/l Mineral Yağ</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>CEVİZ</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Dut kabuklubiti</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Pseudaulacaspis pentagona</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>1000 ml/100 L su</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>İnsektisit</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -3023,12 +3023,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3140,29 +3140,29 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,22 +3209,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,14 +3388,14 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -543,47 +543,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -605,47 +605,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,47 +667,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Pythium spp., Rhizoctonia spp.</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -791,47 +791,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>APRIN XL 350 ES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>350 g/l Metalaxyl-m</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Toprak kökenli patojenler</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>50 ml/100 kg tohum</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>3 mg/kg</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -915,47 +915,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -977,47 +977,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1054,22 +1054,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,52 +1101,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1163,47 +1163,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1287,47 +1287,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1349,47 +1349,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>APRIN XL 350 ES</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>350 g/l Metalaxyl-m</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Toprak kökenli patojenler</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fusarium spp., Macrophomina spp., Phytophthora spp., Rhizoctonia spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>50 ml/100 kg tohum</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1798,22 +1798,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2108,32 +2108,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2217,52 +2217,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2294,22 +2294,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2480,22 +2480,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2899,32 +2899,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TURUNÇGİLLER</t>
+          <t>AYÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Topak unlubiti</t>
+          <t>Külleme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nipaecoccus viridis</t>
+          <t>Erysiphe cichoracearum</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1500 ml/ 100 L su</t>
+          <t>500 g/da</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2944,49 +2944,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
+          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3115,17 +3115,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3147,22 +3147,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3209,12 +3209,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3239,17 +3239,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3264,14 +3264,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,29 +3326,29 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3388,29 +3388,29 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4511,32 +4511,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
@@ -4635,17 +4635,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4690,24 +4690,24 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4759,17 +4759,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4883,17 +4883,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4945,17 +4945,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5069,17 +5069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5193,17 +5193,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5255,32 +5255,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5300,34 +5300,34 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">

--- a/syngenta_bku_live.xlsx
+++ b/syngenta_bku_live.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,52 +915,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7 Gün</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>15 ml/da</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1101,52 +1101,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>15 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1178,22 +1178,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>LATİN ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -1240,32 +1240,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>ELEKTRİK ÇİÇEĞİ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45ml/da</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1302,22 +1302,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MENEKŞE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>SAP KEREVİZİ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>YAPRAK LEKESİ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Cercospora sp.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14 Gün</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
         </is>
       </c>
     </row>
@@ -1426,22 +1426,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1488,22 +1488,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mildiyö</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plasmopara spp, Bremia lactucae</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1674,32 +1674,32 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1736,22 +1736,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ISPANAK</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Erysiphe spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1798,32 +1798,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10 mg / kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MAYDANOZ</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1922,32 +1922,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1984,22 +1984,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>ISPANAK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Erysiphe spp.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ROKA</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>10 mg / kg</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TERE</t>
+          <t>MAYDANOZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alternaria yaprak lekesi</t>
+          <t>Mildiyö</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Alternaria spp.</t>
+          <t>Plasmopara spp, Bremia lactucae</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10 mg/kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2170,17 +2170,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEMİZOTU</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15 mg / kg</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEREOTU</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45 ml / da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70 mg / kg</t>
+          <t>15 mg/kg</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NANE</t>
+          <t>ROKA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>TERE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>10 mg/kg</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2418,17 +2418,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>SEMİZOTU</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sebzelerde septorya yaprak lekesi</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>15 mg / kg</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2480,27 +2480,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FESLEĞEN</t>
+          <t>DEREOTU</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MİLDİYÖ</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>(Peronospora belbahrii)</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45 ml/da</t>
+          <t>45 ml / da</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LATİN ÇİÇEĞİ</t>
+          <t>NANE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Yaprağı Yenen Sebzelerde Beyaz Pas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Albugo candida, Wilsoniana occidentalis, Wilsoniana portulacae</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Latin Çiçeği için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2604,27 +2604,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ELEKTRİK ÇİÇEĞİ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Alternaria yaprak lekesi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Alternaria spp.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>45ml/da</t>
+          <t>45 ml/da</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2666,22 +2666,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MENEKŞE</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Sebzelerde septorya yaprak lekesi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Septoria apiicola, S.lycopersici, S.petroselini</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>70 mg/kg</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni yenilebilir Menekşe için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2728,22 +2728,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SAP KEREVİZİ</t>
+          <t>FESLEĞEN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>YAPRAK LEKESİ</t>
+          <t>MİLDİYÖ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cercospora sp.</t>
+          <t>(Peronospora belbahrii)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>14 Gün</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>70 mg/kg</t>
+          <t>70 mg / kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Bu geçici kullanım izni Sap Kereviz için Antalya ve Burdur illerinde geçerli olacak şekilde düzenlenmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2899,32 +2899,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AYÇİÇEĞİ</t>
+          <t>TURUNÇGİLLER</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Külleme</t>
+          <t>Topak unlubiti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Erysiphe cichoracearum</t>
+          <t>Nipaecoccus viridis</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>500 g/da</t>
+          <t>1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2944,79 +2944,79 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit+Akarisit</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Ege Bölgesi illeri için geçici kullanım izni verilmiştir.</t>
+          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>NİNJA 5 EC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TURUNÇGİLLER</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Topak unlubiti</t>
+          <t>Turunçgil uzun antenli böceği</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nipaecoccus viridis</t>
+          <t>Anoplophora chinensis</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1500 ml/ 100 L su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>İnsektisit+Akarisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>* Mineral yağ uygulamalarında sıcaklığın 32°C’nin altında olduğu serin saatleri (sabah erken veya akşamüzeri) tercih edilmesi gerekmektedir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>ELMA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 l su</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ELMA</t>
+          <t>ARMUT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3147,12 +3147,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NİNJA 5 EC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ARMUT</t>
+          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>20 ml/100 l su</t>
+          <t>30 ml/100 L  su</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3202,24 +3202,24 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>30 ml/100 L  su</t>
+          <t>25 ml/100 L  su</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3271,22 +3271,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>AMPLİGO 150 ZC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ZC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAVAK, ÇINAR, HUŞ, AT KESTANESİ, KARAAĞAÇ, KIZILAĞAÇ, AKÇAAĞAÇ, GÜRGEN</t>
+          <t>FINDIK</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 gün</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>25 ml/100 L  su</t>
+          <t>45 ml/100 L. su</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Muğla- Kocaeli-İstanbul-Trabzon-Sakarya-Antalya-Diyarbakır-Rize illerindeki karantina amaçlı kullanılacak mücadele için geçici kullanım izni verilmiştir.</t>
+          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FINDIK</t>
+          <t>KİRAZ</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7 gün</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>45 ml/100 L. su</t>
+          <t>50 ml/100 l su</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0.03 Lambda-cyhalothrin:0.01</t>
+          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KİRAZ</t>
+          <t>BADEM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Turunçgil uzun antenli böceği</t>
+          <t>Dipkurtları</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anoplophora chinensis</t>
+          <t>Capnodis spp.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda-cyhalothrin:0.3</t>
+          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Muğla-Kocaeli-İstanbul- Trabzon-Sakarya-Antalya-Diyarbakır- Rize İlleri için verilmiştir.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BADEM</t>
+          <t>KAYISI</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:0,03 Lambda cyhalothrin:0,01*</t>
+          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3519,32 +3519,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AMPLİGO 150 ZC</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>100 g/l Chlorantraniliprole + 50 g/l Lambda-cyhalothrin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KAYISI</t>
+          <t>ALIÇ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dipkurtları</t>
+          <t>Elma içkurdu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Capnodis spp.</t>
+          <t>Cydia pomonella</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50 ml/100 l su</t>
+          <t>20 ml/100 L su</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Chlorantraniliprole:1 Lambda cyhalothrin:0,15</t>
+          <t>0,2 (mg/kg)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3596,32 +3596,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ALIÇ</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Elma içkurdu</t>
+          <t>Danaburnu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cydia pomonella</t>
+          <t>Gryllotalpa gryllotalpa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>21 gün</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>20 ml/100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0,2 (mg/kg)</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KAVUN</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KABAK</t>
+          <t>KARPUZ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,06</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BAMYA</t>
+          <t xml:space="preserve">LAHANA </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0,3 mg/kg</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>KAVUN</t>
+          <t>MARUL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KARPUZ</t>
+          <t>PATATES</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,01*</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LAHANA </t>
+          <t>DOMATES</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>MARUL</t>
+          <t>BİBER</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PATATES</t>
+          <t>HIYAR</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>0,01*</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DOMATES</t>
+          <t>KABAK</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BİBER</t>
+          <t>BAMYA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,3 mg/kg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Çiçek bamyasında PHI sürelerine dikkat edilerek hasat yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HIYAR</t>
+          <t>PATLICAN</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4325,47 +4325,47 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PATLICAN</t>
+          <t>FASULYE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Danaburnu</t>
+          <t>KÜLLEME</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gryllotalpa gryllotalpa</t>
+          <t>Erysiphe polygoni</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>21 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>300 g/100 L su</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4375,29 +4375,29 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4417,17 +4417,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14 gün</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>300 g/100 L su</t>
+          <t>80-100 ml/da</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>*Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>QUADRİS MAXX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4459,69 +4459,69 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>FASULYE</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KÜLLEME</t>
+          <t>Süs bitkilerinde pas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Erysiphe polygoni</t>
+          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>14 gün</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>80-100 ml/da</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0260010  Kabuklu: 3; 0260020 Kabuksuz: 3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>IMPERATOR 25 EC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t>250 g/l Cypermethrin</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
+          <t>ÇEKİRGELER</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Coccoidea</t>
+          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1000 – 1500 ml/ 100 L su</t>
+          <t>40 ml/da</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4566,39 +4566,39 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PLOCAFİR</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>700 g/l Mineral Yağ</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AHUDUDU VE BÖĞÜRTLEN</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Turunçgil unlubiti</t>
+          <t>Bozkurt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Planococcus citri</t>
+          <t>Agrotis spp.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1000 ml/100 l su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4628,24 +4628,24 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde yaprak leke hastalığı</t>
+          <t>Telkurtları</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
+          <t>Agriotes spp.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>40 ml/100 L su</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4697,17 +4697,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUADRİS</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>250 g/l Azoxystrobin</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde mildiyö</t>
+          <t>Bağ maymuncukları</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Peronospora spp., Phytophthora spp.</t>
+          <t>Otiorhynchus spp.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>100 ml/100 L su</t>
+          <t>25 ml/100 L su</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fungisit</t>
+          <t>İnsektisit</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4759,17 +4759,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>KARATE ZEON</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>15 ml/100 L su</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4821,32 +4821,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PROCLAIM 05 SG</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>%5 Emamectin benzoate</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>AHUDUDU VE BÖĞÜRTLEN</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yeşilkurt</t>
+          <t>Turunçgil unlubiti</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helicoverpa armigera</t>
+          <t>Planococcus citri</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>150 g/100 L su (1 da alan için)</t>
+          <t>1000 ml/100 l su</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4876,24 +4876,24 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IMPERATOR 25 EC</t>
+          <t>PLOCAFİR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>250 g/l Cypermethrin</t>
+          <t>700 g/l Mineral Yağ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ÇEKİRGELER</t>
+          <t>Süs bitkilerinde kabuklu bit ve koşniller</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Acrididae, Catantopidae, Tettigoniidae, Grylidae</t>
+          <t>Coccoidea</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>40 ml/da</t>
+          <t>1000 – 1500 ml/ 100 L su</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4938,14 +4938,14 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır. ***Bitki koruma ürünü etiketinde yer alan kullanım şekillerine ve uyarılara dikkat edilmelidir!</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUADRİS MAXX</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>200 g/l Azoxystrobin + 125 g/l Difenoconazole</t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Süs bitkilerinde pas</t>
+          <t>Süs bitkilerinde yaprak leke hastalığı</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Phragmadium mucronatum, Uromyces spp., Puccinia spp.</t>
+          <t>Alternaria spp., Septoria spp., Cercospora spp.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5007,17 +5007,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>QUADRİS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>250 g/l Azoxystrobin</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5027,12 +5027,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pamuk yaprakkurdu</t>
+          <t>Süs bitkilerinde mildiyö</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spodoptera littoralis</t>
+          <t>Peronospora spp., Phytophthora spp.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>15 ml/100 L su</t>
+          <t>100 ml/100 L su</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5069,17 +5069,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bozkurt</t>
+          <t>Pamuk yaprakkurdu</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Agrotis spp.</t>
+          <t>Spodoptera littoralis</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5131,17 +5131,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>PROCLAIM 05 SG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%5 Emamectin benzoate</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Telkurtları</t>
+          <t>Yeşilkurt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Agriotes spp.</t>
+          <t>Helicoverpa armigera</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>40 ml/100 L su</t>
+          <t>150 g/100 L su (1 da alan için)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5193,32 +5193,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>KARATE ZEON</t>
+          <t>THIOVIT JET</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">50 g/l Lambda-cyhalothrin </t>
+          <t>%80 Kükürt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİ</t>
+          <t>BİBER (tarla)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bağ maymuncukları</t>
+          <t>İki noktalı kırmızıörümcek</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Otiorhynchus spp.</t>
+          <t>Tetranychus urticae</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>25 ml/100 L su</t>
+          <t>80-200 g/da</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-01</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
+          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -5270,17 +5270,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BİBER (tarla)</t>
+          <t>SÜS BİTKİLERİ</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>İki noktalı kırmızıörümcek</t>
+          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tetranychus urticae</t>
+          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>80-200 g/da</t>
+          <t>300 – 400 g/100 L su</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5300,24 +5300,24 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>İnsektisit</t>
+          <t>Fungisit</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-11-01</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Etikette yer alan kullanım uyarılarına dikkat edilmelidir. Akşam serininde 30 C altı sıcaklıklarda uygulama yapılmalıdır.</t>
+          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>THIOVIT JET</t>
+          <t>SWITCH 62.5 WG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>%80 Kükürt</t>
+          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SÜS BİTKİLERİNDE KÜLLEME</t>
+          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Erysiphe spp., Podosphaera spp., Phyllactinia spp., Uncinula spp., Sphaerotheca spp., Microsphaera spp., Oidium spp. ve Leveillula spp.</t>
+          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>300 – 400 g/100 L su</t>
+          <t>30 g/100 L su</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5371,68 +5371,6 @@
         </is>
       </c>
       <c r="L80" t="inlineStr">
-        <is>
-          <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>SWITCH 62.5 WG</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>WG</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>%37,5 Cyprodinil + %25 Fludioxonil</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>SÜS BİTKİLERİ</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Süs bitkilerinde fungal kök çürüklüğü ve solgunluk</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Fusarium spp., Rhizoctonia spp., Pythium spp., Sclerotonia sclerotiorum, Verticillium spp.</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>30 g/100 L su</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Fungisit</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
         <is>
           <t>*Fitotoksik etkilerin gözlemlenmesi için öncelikle küçük bir alanda veya az sayıda bitki üzerinde deneyiniz! **Süs bitkileri yetiştiriciliği amacı dışında yapılan her türlü yetiştiricilik faaliyeti için (Gıda, Kozmetik, Eczacılık vb.) çizelgede önerilen aktif maddeleri içeren bitki koruma ürünleri kesinlikle kullanılmamalıdır. Bu nedenle PHI ve MRL belirlenmemiştir. Ancak, uygulayıcı maruziyeti açısından etikette yer alan güvenlik önlemlerine uyulmalıdır.</t>
         </is>
